--- a/PD_LTSF_Campaign_Plan.xlsx
+++ b/PD_LTSF_Campaign_Plan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="344">
   <si>
     <t xml:space="preserve">Prime Big Deal Days: LTSF clearance campaigns</t>
   </si>
@@ -39,7 +39,10 @@
     <t xml:space="preserve">When: start 6 Oct 2026, end 7 Oct 2026 (PD days only). The end date is set on each campaign, so they stop on their own. Existing campaigns are unchanged.</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget: each campaign's daily budget is about 2x the product's current daily ad spend on these SKUs, with a minimum of $25 (US) or C$20 (CA).</t>
+    <t xml:space="preserve">Bids: capped at each product's PD break-even CPC (deal margin per unit x 30-day conversion rate x 1.5 for the PD lift), so ad-driven sales do not lose money. Auto: close-match at break-even, then loose 90%, substitutes 80%, complements 60%. Broad: Amazon's suggested bid, never above break-even.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget: each campaign's daily budget is about 2x the product's current daily ad spend on these SKUs, with a minimum of $25 (US) or C$20 (CA). With bids held at break-even, campaigns may not use their full budget.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources: aged units and the 15-Oct estimate come from the LTSF engine (Amazon age snapshot 3 Oct). Spend and billed LTSF come from Sellerboard (6 Sep–5 Oct). Deals come from the PD allocation planner. CA figures are in CAD; Sellerboard USD is converted at 1.38.</t>
@@ -177,7 +180,7 @@
     <t xml:space="preserve">n/a (auto)</t>
   </si>
   <si>
-    <t xml:space="preserve">close 1.42 / loose 1.28 / subs 1.14 / comp 0.85</t>
+    <t xml:space="preserve">close 1.45 / loose 1.30 / subs 1.16 / comp 0.87</t>
   </si>
   <si>
     <t xml:space="preserve">Dynamic bids - down only</t>
@@ -210,13 +213,13 @@
     <t xml:space="preserve">Amazon suggested keywords (selected in console)</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 3.21 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 1.45 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">DBS6-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
   </si>
   <si>
-    <t xml:space="preserve">close 1.47 / loose 1.32 / subs 1.18 / comp 0.88</t>
+    <t xml:space="preserve">close 1.50 / loose 1.35 / subs 1.20 / comp 0.90</t>
   </si>
   <si>
     <t xml:space="preserve">BAMBOO-FULL-OLIVE-6PCS, BAMBOO-FULL-CREME-6PCS, BAMBOO-QUEEN-OLIVE-6PCS, BAMBOO-QUEEN-LIGHTOLIVE-6PCS, BAMBOO-QUEEN-LIGHTGREY-6PCS, BAMBOO-FULL-LIGHTOLIVE-6PCS, BAMBOO-FULL-SAGE GREEN-6PCS, BAMBOO-KING-PURPLE-6PCS, BAMBOO-KING-LIGHT PINK-6PCS, BAMBOO-QUEEN-SAGE GREEN-6PCS, BAMBOO-TWIN-LIGHTOLIVE-6PCS, BAMBOO-FULL-PURPLE-6PCS, BAMBOO-TWIN-MIDGREY-6PCS, BAMBOO-TWIN-SAGE GREEN-6PCS, BAMBOO-TWIN-OLIVE-6PCS, BAMBOO-TWIN-NAVYBLUE-6PCS</t>
@@ -225,13 +228,13 @@
     <t xml:space="preserve">DBS6-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 3.06 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 1.50 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">DSS4-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
   </si>
   <si>
-    <t xml:space="preserve">close 0.72 / loose 0.65 / subs 0.58 / comp 0.43</t>
+    <t xml:space="preserve">close 0.45 / loose 0.41 / subs 0.36 / comp 0.27</t>
   </si>
   <si>
     <t xml:space="preserve">SATIN-QUEEN-GREY, SATIN-SEA-TEAL-TWIN, SATIN-4PC-FULL-DARK GREEN, SATIN-4PCS-FULL-ROSEWOOD, SATIN-TAUPE-FULL, SATIN-STRIPE-FULL-GOLD, SATIN-3PC-TWIN-DARK GREEN, SATIN-IVORY-FULL, SATIN-TWIN-GREY, SATIN-4PC-KING-GREY, SATIN-3PC-TWIN-BURNT ORANGE, SATIN-STRIPE-FULL-PURPLE, SATIN-FULL-GREY, SATIN-STRIPE-TWIN-BLACK, SATIN-CHAMPAGNE-TWIN, SATIN-STRIPE-TWIN-RED, SATIN-IVORY-TWIN, SATIN-4PC-TWIN-DARK GREEN, SATIN-4PC-TWIN-BURNT ORANGE, SATIN-3PC-TWIN-SAGE GREEN, SATIN-STONEGREY-TWIN, SATIN-RED-TWIN, SATIN-STRIPE-TWIN-PURPLE, SATIN-STRIPE-TWIN-BLUE, SATIN-STRIPE-TWIN-WHITE, SATIN-4PC-TWIN-BLUSH PINK, SATIN-CHAMPAGNE-FULL, SATIN-STONEGREY-FULL, SATIN-3PC-TWIN-NAVY BLUE, SATIN-TWIN-BLUE, SATIN-4PC-TWIN-LAVENDER, SATIN-STRIPE-FULL-GRAY, SATIN-STRIPE-TWIN-PINK, SATIN-GOLD-TWIN</t>
@@ -240,7 +243,7 @@
     <t xml:space="preserve">DSS4-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 1.65 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 0.45 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">D-SPC-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
@@ -255,7 +258,7 @@
     <t xml:space="preserve">D-SPC-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 1.32 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 0.75 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">DBS4-CA-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
@@ -264,7 +267,7 @@
     <t xml:space="preserve">Bulk upload (PD_LTSF_Auto_Bulk_CA.xlsx)</t>
   </si>
   <si>
-    <t xml:space="preserve">close 2.02 / loose 1.82 / subs 1.62 / comp 1.21</t>
+    <t xml:space="preserve">close 1.40 / loose 1.26 / subs 1.12 / comp 0.84</t>
   </si>
   <si>
     <t xml:space="preserve">BAMBOO-QUEEN-OLIVE, BAMBOO-CALIFKING-LIGHTGREY, BAMBOO-CALIFKING-MIDGREY, BAMBOO-CALIFKING-CREME, BAMBOO-QUEEN-LIGHTGREY, BAMBOO-FULL-OLIVE, BAMBOO-KING-LIGHTBLUE</t>
@@ -273,25 +276,28 @@
     <t xml:space="preserve">DBS4-CA-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 1.78 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 1.40 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">DBS6-CA-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
   </si>
   <si>
+    <t xml:space="preserve">close 1.30 / loose 1.17 / subs 1.04 / comp 0.78</t>
+  </si>
+  <si>
     <t xml:space="preserve">BAMBOO-CALIFKING-NAVYBLUE-6PCS, BAMBOO-QUEEN-LIGHTOLIVE-6PCS, BAMBOO-CALIFKING-LIGHTBLUE-6PCS, BAMBOO-KING-LIGHTBLUE-6PCS, BAMBOO-CALIFKING-GREY-6PCS</t>
   </si>
   <si>
     <t xml:space="preserve">DBS6-CA-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 2.50 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 1.30 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">DSS4-CA-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
   </si>
   <si>
-    <t xml:space="preserve">close 1.17 / loose 1.05 / subs 0.94 / comp 0.70</t>
+    <t xml:space="preserve">close 0.70 / loose 0.63 / subs 0.56 / comp 0.42</t>
   </si>
   <si>
     <t xml:space="preserve">SATIN-4PC-KING-GREY, SATIN-STRIPE-FULL-WHITE</t>
@@ -300,13 +306,13 @@
     <t xml:space="preserve">DSS4-CA-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 1.23 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 0.70 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">DSS6-CA-SP-AUTO-(PD-LTSF)-Aged Deal SKUs</t>
   </si>
   <si>
-    <t xml:space="preserve">close 1.20 / loose 1.08 / subs 0.96 / comp 0.72</t>
+    <t xml:space="preserve">close 0.65 / loose 0.59 / subs 0.52 / comp 0.39</t>
   </si>
   <si>
     <t xml:space="preserve">SATIN-GOLD-KING-6PCS, SATIN-STRIPE-FULL-BLACK--6-PCS, SATIN-STRIPE-QUEEN-PINK--6-PCS, SATIN-STRIPE-TWIN-BLACK--6-PCS, SATIN-STONEGREY-QUEEN-6PCS, SATIN-GOLD-QUEEN-6PCS, SATIN-KING-PINK-6PCS, SATIN-6PC-FULL-NAVY BLUE, SATIN-6PC-QUEEN-BLUSH PINK, SATIN-6PC-FULL-LAVENDER</t>
@@ -315,7 +321,7 @@
     <t xml:space="preserve">DSS6-CA-SP-BROAD-(PD-LTSF)-Amazon Suggested</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon suggested bid, capped at 1.29 (product's 30-day avg CPC)</t>
+    <t xml:space="preserve">Amazon suggested bid, capped at 0.65 (PD break-even CPC)</t>
   </si>
   <si>
     <t xml:space="preserve">Auto campaign</t>
@@ -1532,7 +1538,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1617,326 +1623,297 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>878</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>533</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>899.59</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>977.46</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>6938.54</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>228</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>463</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <f aca="false">J10+K10</f>
-        <v>926</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1534</v>
+        <v>878</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1218</v>
+        <v>533</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2383.94</v>
+        <v>899.59</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1679.43</v>
+        <v>977.46</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3335.98</v>
+        <v>6938.54</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>222</v>
+        <v>463</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>222</v>
+        <v>463</v>
       </c>
       <c r="L11" s="5" t="n">
         <f aca="false">J11+K11</f>
-        <v>444</v>
+        <v>926</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2339</v>
+        <v>1534</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>606</v>
+        <v>1218</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1224.5</v>
+        <v>2383.94</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1034.12</v>
+        <v>1679.43</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>5244.58</v>
+        <v>3335.98</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>590</v>
+        <v>257</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>350</v>
+        <v>222</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>350</v>
+        <v>222</v>
       </c>
       <c r="L12" s="5" t="n">
         <f aca="false">J12+K12</f>
-        <v>700</v>
+        <v>444</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1929</v>
+        <v>2339</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1752</v>
+        <v>606</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>406.93</v>
+        <v>1224.5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>268.36</v>
+        <v>1034.12</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>643.67</v>
+        <v>5244.58</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>110</v>
+        <v>590</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>43</v>
+        <v>350</v>
       </c>
       <c r="L13" s="5" t="n">
         <f aca="false">J13+K13</f>
-        <v>86</v>
+        <v>700</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="C14" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>91</v>
+        <v>1929</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>78</v>
+        <v>1752</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>192.21</v>
+        <v>406.93</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>128.05</v>
+        <v>268.36</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1449.66</v>
+        <v>643.67</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="L14" s="5" t="n">
         <f aca="false">J14+K14</f>
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>55.39</v>
+        <v>192.21</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>73.42</v>
+        <v>128.05</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6.6</v>
+        <v>1449.66</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="L15" s="5" t="n">
         <f aca="false">J15+K15</f>
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.7</v>
+        <v>55.39</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>73.42</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>141.79</v>
+        <v>6.6</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>20</v>
@@ -1949,165 +1926,208 @@
         <v>40</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="I17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>123.19</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>105.18</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>394.82</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>50</v>
-      </c>
       <c r="J17" s="5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L17" s="5" t="n">
         <f aca="false">J17+K17</f>
+        <v>40</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>123.19</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>105.18</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>394.82</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <f aca="false">J18+K18</f>
         <v>52</v>
       </c>
-      <c r="M17" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <f aca="false">SUMIFS(C10:C17,$A$10:$A$17,"US")</f>
-        <v>76</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <f aca="false">SUMIFS(D10:D17,$A$10:$A$17,"US")</f>
-        <v>6680</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <f aca="false">SUMIFS(E10:E17,$A$10:$A$17,"US")</f>
-        <v>4109</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <f aca="false">SUMIFS(F10:F17,$A$10:$A$17,"US")</f>
-        <v>4914.96</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <f aca="false">SUMIFS(G10:G17,$A$10:$A$17,"US")</f>
-        <v>3959.37</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <f aca="false">SUMIFS(H10:H17,$A$10:$A$17,"US")</f>
-        <v>16162.77</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <f aca="false">SUMIFS(I10:I17,$A$10:$A$17,"US")</f>
-        <v>1185</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <f aca="false">SUMIFS(J10:J17,$A$10:$A$17,"US")</f>
-        <v>1078</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <f aca="false">SUMIFS(K10:K17,$A$10:$A$17,"US")</f>
-        <v>1078</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <f aca="false">SUMIFS(L10:L17,$A$10:$A$17,"US")</f>
-        <v>2156</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>21</v>
+      <c r="M18" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="8" t="n">
-        <f aca="false">SUMIFS(C10:C17,$A$10:$A$17,"CA")</f>
+        <f aca="false">SUMIFS(C11:C18,$A$11:$A$18,"US")</f>
+        <v>76</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <f aca="false">SUMIFS(D11:D18,$A$11:$A$18,"US")</f>
+        <v>6680</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <f aca="false">SUMIFS(E11:E18,$A$11:$A$18,"US")</f>
+        <v>4109</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <f aca="false">SUMIFS(F11:F18,$A$11:$A$18,"US")</f>
+        <v>4914.96</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <f aca="false">SUMIFS(G11:G18,$A$11:$A$18,"US")</f>
+        <v>3959.37</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <f aca="false">SUMIFS(H11:H18,$A$11:$A$18,"US")</f>
+        <v>16162.77</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <f aca="false">SUMIFS(I11:I18,$A$11:$A$18,"US")</f>
+        <v>1185</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <f aca="false">SUMIFS(J11:J18,$A$11:$A$18,"US")</f>
+        <v>1078</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <f aca="false">SUMIFS(K11:K18,$A$11:$A$18,"US")</f>
+        <v>1078</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <f aca="false">SUMIFS(L11:L18,$A$11:$A$18,"US")</f>
+        <v>2156</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <f aca="false">SUMIFS(C11:C18,$A$11:$A$18,"CA")</f>
         <v>24</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <f aca="false">SUMIFS(D10:D17,$A$10:$A$17,"CA")</f>
+      <c r="D20" s="8" t="n">
+        <f aca="false">SUMIFS(D11:D18,$A$11:$A$18,"CA")</f>
         <v>276</v>
       </c>
-      <c r="E19" s="8" t="n">
-        <f aca="false">SUMIFS(E10:E17,$A$10:$A$17,"CA")</f>
+      <c r="E20" s="8" t="n">
+        <f aca="false">SUMIFS(E11:E18,$A$11:$A$18,"CA")</f>
         <v>205</v>
       </c>
-      <c r="F19" s="9" t="n">
-        <f aca="false">SUMIFS(F10:F17,$A$10:$A$17,"CA")</f>
+      <c r="F20" s="9" t="n">
+        <f aca="false">SUMIFS(F11:F18,$A$11:$A$18,"CA")</f>
         <v>371.49</v>
       </c>
-      <c r="G19" s="9" t="n">
-        <f aca="false">SUMIFS(G10:G17,$A$10:$A$17,"CA")</f>
+      <c r="G20" s="9" t="n">
+        <f aca="false">SUMIFS(G11:G18,$A$11:$A$18,"CA")</f>
         <v>306.65</v>
       </c>
-      <c r="H19" s="9" t="n">
-        <f aca="false">SUMIFS(H10:H17,$A$10:$A$17,"CA")</f>
+      <c r="H20" s="9" t="n">
+        <f aca="false">SUMIFS(H11:H18,$A$11:$A$18,"CA")</f>
         <v>1992.87</v>
       </c>
-      <c r="I19" s="8" t="n">
-        <f aca="false">SUMIFS(I10:I17,$A$10:$A$17,"CA")</f>
+      <c r="I20" s="8" t="n">
+        <f aca="false">SUMIFS(I11:I18,$A$11:$A$18,"CA")</f>
         <v>148</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <f aca="false">SUMIFS(J10:J17,$A$10:$A$17,"CA")</f>
+      <c r="J20" s="8" t="n">
+        <f aca="false">SUMIFS(J11:J18,$A$11:$A$18,"CA")</f>
         <v>163</v>
       </c>
-      <c r="K19" s="8" t="n">
-        <f aca="false">SUMIFS(K10:K17,$A$10:$A$17,"CA")</f>
+      <c r="K20" s="8" t="n">
+        <f aca="false">SUMIFS(K11:K18,$A$11:$A$18,"CA")</f>
         <v>163</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <f aca="false">SUMIFS(L10:L17,$A$10:$A$17,"CA")</f>
+      <c r="L20" s="8" t="n">
+        <f aca="false">SUMIFS(L11:L18,$A$11:$A$18,"CA")</f>
         <v>326</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>30</v>
+      <c r="M20" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A8:I8"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2149,64 +2169,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2214,52 +2234,52 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="11" t="n">
         <v>463</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2" s="11" t="n">
         <v>15</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R2" s="11" t="n">
         <v>878</v>
@@ -2276,52 +2296,52 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J3" s="13" t="n">
         <v>463</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3" s="13" t="n">
         <v>15</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R3" s="13" t="n">
         <v>878</v>
@@ -2338,52 +2358,52 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J4" s="11" t="n">
         <v>222</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P4" s="11" t="n">
         <v>16</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R4" s="11" t="n">
         <v>1534</v>
@@ -2400,52 +2420,52 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="13" t="n">
         <v>222</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5" s="13" t="n">
         <v>16</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R5" s="13" t="n">
         <v>1534</v>
@@ -2462,52 +2482,52 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="11" t="n">
         <v>350</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P6" s="11" t="n">
         <v>34</v>
       </c>
       <c r="Q6" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R6" s="11" t="n">
         <v>2339</v>
@@ -2524,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7" s="13" t="n">
         <v>350</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P7" s="13" t="n">
         <v>34</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R7" s="13" t="n">
         <v>2339</v>
@@ -2586,52 +2606,52 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>43</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P8" s="11" t="n">
         <v>11</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R8" s="11" t="n">
         <v>1929</v>
@@ -2648,52 +2668,52 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J9" s="13" t="n">
         <v>43</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O9" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P9" s="13" t="n">
         <v>11</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R9" s="13" t="n">
         <v>1929</v>
@@ -2710,52 +2730,52 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>97</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O10" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P10" s="11" t="n">
         <v>7</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R10" s="11" t="n">
         <v>91</v>
@@ -2772,52 +2792,52 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" s="13" t="n">
         <v>97</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P11" s="13" t="n">
         <v>7</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>91</v>
@@ -2834,52 +2854,52 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P12" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R12" s="11" t="n">
         <v>32</v>
@@ -2896,52 +2916,52 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J13" s="13" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P13" s="13" t="n">
         <v>5</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>32</v>
@@ -2958,52 +2978,52 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P14" s="11" t="n">
         <v>2</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R14" s="11" t="n">
         <v>4</v>
@@ -3020,52 +3040,52 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J15" s="13" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O15" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="Q15" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>4</v>
@@ -3082,52 +3102,52 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>26</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O16" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P16" s="11" t="n">
         <v>10</v>
       </c>
       <c r="Q16" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R16" s="11" t="n">
         <v>149</v>
@@ -3144,52 +3164,52 @@
         <v>16</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J17" s="13" t="n">
         <v>26</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P17" s="13" t="n">
         <v>10</v>
       </c>
       <c r="Q17" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>149</v>
@@ -3235,69 +3255,69 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>10</v>
@@ -3318,30 +3338,30 @@
         <v>542.5</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>10</v>
@@ -3362,30 +3382,30 @@
         <v>1029.62</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>10</v>
@@ -3406,30 +3426,30 @@
         <v>796.93</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>10</v>
@@ -3450,30 +3470,30 @@
         <v>250.68</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>10</v>
@@ -3494,30 +3514,30 @@
         <v>104.11</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>16</v>
@@ -3538,30 +3558,30 @@
         <v>1591.62</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>10</v>
@@ -3582,30 +3602,30 @@
         <v>64.47</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>10</v>
@@ -3626,30 +3646,30 @@
         <v>202.71</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>36</v>
@@ -3670,30 +3690,30 @@
         <v>1003.62</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>36</v>
@@ -3714,30 +3734,30 @@
         <v>397.4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>30</v>
@@ -3758,30 +3778,30 @@
         <v>381.84</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>10</v>
@@ -3802,30 +3822,30 @@
         <v>171.03</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>10</v>
@@ -3846,30 +3866,30 @@
         <v>56.3</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>10</v>
@@ -3890,30 +3910,30 @@
         <v>125.95</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>10</v>
@@ -3934,30 +3954,30 @@
         <v>219.76</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>10</v>
@@ -3978,30 +3998,30 @@
         <v>8.09</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>19</v>
@@ -4022,30 +4042,30 @@
         <v>0</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>48</v>
@@ -4066,30 +4086,30 @@
         <v>2958.25</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>10</v>
@@ -4110,30 +4130,30 @@
         <v>16.82</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>31</v>
@@ -4154,30 +4174,30 @@
         <v>12.69</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>10</v>
@@ -4198,30 +4218,30 @@
         <v>0</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>10</v>
@@ -4242,30 +4262,30 @@
         <v>2.25</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>23</v>
@@ -4286,30 +4306,30 @@
         <v>145.08</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>15</v>
@@ -4330,30 +4350,30 @@
         <v>63.1</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>21</v>
@@ -4374,30 +4394,30 @@
         <v>0</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>10</v>
@@ -4418,30 +4438,30 @@
         <v>0</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>10</v>
@@ -4462,30 +4482,30 @@
         <v>3.25</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>10</v>
@@ -4506,30 +4526,30 @@
         <v>0</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>10</v>
@@ -4550,30 +4570,30 @@
         <v>125.55</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>10</v>
@@ -4594,30 +4614,30 @@
         <v>0.9</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>10</v>
@@ -4638,30 +4658,30 @@
         <v>0</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>41</v>
@@ -4682,30 +4702,30 @@
         <v>1702.77</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>10</v>
@@ -4726,30 +4746,30 @@
         <v>6.41</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>20</v>
@@ -4770,30 +4790,30 @@
         <v>5.7</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>10</v>
@@ -4814,30 +4834,30 @@
         <v>197.46</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>10</v>
@@ -4858,30 +4878,30 @@
         <v>0.6</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>20</v>
@@ -4902,30 +4922,30 @@
         <v>61.52</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>20</v>
@@ -4946,30 +4966,30 @@
         <v>4.4</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>20</v>
@@ -4990,30 +5010,30 @@
         <v>0.5</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>20</v>
@@ -5034,30 +5054,30 @@
         <v>39.41</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>39</v>
@@ -5078,30 +5098,30 @@
         <v>2894.55</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>20</v>
@@ -5122,30 +5142,30 @@
         <v>9.82</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>20</v>
@@ -5166,30 +5186,30 @@
         <v>0</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>20</v>
@@ -5210,30 +5230,30 @@
         <v>209.3</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>10</v>
@@ -5254,30 +5274,30 @@
         <v>2.9</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>220</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>10</v>
@@ -5298,30 +5318,30 @@
         <v>0</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>20</v>
@@ -5342,30 +5362,30 @@
         <v>11.24</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>20</v>
@@ -5386,30 +5406,30 @@
         <v>1.47</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>20</v>
@@ -5430,30 +5450,30 @@
         <v>5.2</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>20</v>
@@ -5474,30 +5494,30 @@
         <v>4.53</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>20</v>
@@ -5518,30 +5538,30 @@
         <v>4.28</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H53" s="4" t="n">
         <v>20</v>
@@ -5562,30 +5582,30 @@
         <v>0</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H54" s="4" t="n">
         <v>10</v>
@@ -5606,30 +5626,30 @@
         <v>8.42</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>10</v>
@@ -5650,30 +5670,30 @@
         <v>1.35</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H56" s="4" t="n">
         <v>10</v>
@@ -5694,30 +5714,30 @@
         <v>2.27</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H57" s="4" t="n">
         <v>10</v>
@@ -5738,30 +5758,30 @@
         <v>5.08</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>20</v>
@@ -5782,30 +5802,30 @@
         <v>0</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H59" s="4" t="n">
         <v>20</v>
@@ -5826,30 +5846,30 @@
         <v>7.39</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>10</v>
@@ -5870,30 +5890,30 @@
         <v>0.9</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H61" s="4" t="n">
         <v>10</v>
@@ -5914,30 +5934,30 @@
         <v>0</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H62" s="4" t="n">
         <v>10</v>
@@ -5958,30 +5978,30 @@
         <v>45.67</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H63" s="4" t="n">
         <v>20</v>
@@ -6002,30 +6022,30 @@
         <v>3.2</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H64" s="4" t="n">
         <v>10</v>
@@ -6046,30 +6066,30 @@
         <v>2.39</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H65" s="4" t="n">
         <v>20</v>
@@ -6090,30 +6110,30 @@
         <v>1.35</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>20</v>
@@ -6134,30 +6154,30 @@
         <v>4.5</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H67" s="4" t="n">
         <v>10</v>
@@ -6178,30 +6198,30 @@
         <v>3.25</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H68" s="4" t="n">
         <v>10</v>
@@ -6222,30 +6242,30 @@
         <v>2.53</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H69" s="4" t="n">
         <v>10</v>
@@ -6266,30 +6286,30 @@
         <v>7.22</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H70" s="4" t="n">
         <v>10</v>
@@ -6310,30 +6330,30 @@
         <v>0</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H71" s="4" t="n">
         <v>10</v>
@@ -6354,30 +6374,30 @@
         <v>621.11</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H72" s="4" t="n">
         <v>10</v>
@@ -6398,30 +6418,30 @@
         <v>1.95</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H73" s="4" t="n">
         <v>10</v>
@@ -6442,30 +6462,30 @@
         <v>0</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>10</v>
@@ -6486,30 +6506,30 @@
         <v>0.65</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H75" s="4" t="n">
         <v>10</v>
@@ -6530,30 +6550,30 @@
         <v>0.9</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H76" s="4" t="n">
         <v>10</v>
@@ -6574,30 +6594,30 @@
         <v>0</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>10</v>
@@ -6618,30 +6638,30 @@
         <v>6.06</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H78" s="4" t="n">
         <v>10</v>
@@ -6662,30 +6682,30 @@
         <v>1375.06</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H79" s="4" t="n">
         <v>10</v>
@@ -6706,30 +6726,30 @@
         <v>27.93</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H80" s="4" t="n">
         <v>10</v>
@@ -6750,30 +6770,30 @@
         <v>0.5</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F81" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="H81" s="4" t="n">
         <v>10</v>
@@ -6794,30 +6814,30 @@
         <v>32.09</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H82" s="4" t="n">
         <v>5</v>
@@ -6838,30 +6858,30 @@
         <v>0</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H83" s="4" t="n">
         <v>5</v>
@@ -6882,30 +6902,30 @@
         <v>14.09</v>
       </c>
       <c r="N83" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H84" s="4" t="n">
         <v>11</v>
@@ -6926,30 +6946,30 @@
         <v>0</v>
       </c>
       <c r="N84" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>5</v>
@@ -6970,30 +6990,30 @@
         <v>0</v>
       </c>
       <c r="N85" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H86" s="4" t="n">
         <v>5</v>
@@ -7014,30 +7034,30 @@
         <v>1.86</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E87" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="H87" s="4" t="n">
         <v>5</v>
@@ -7058,30 +7078,30 @@
         <v>0</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H88" s="4" t="n">
         <v>7</v>
@@ -7102,30 +7122,30 @@
         <v>4.73</v>
       </c>
       <c r="N88" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H89" s="4" t="n">
         <v>5</v>
@@ -7146,30 +7166,30 @@
         <v>0</v>
       </c>
       <c r="N89" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>5</v>
@@ -7190,30 +7210,30 @@
         <v>124.43</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H91" s="4" t="n">
         <v>5</v>
@@ -7234,30 +7254,30 @@
         <v>17.36</v>
       </c>
       <c r="N91" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H92" s="4" t="n">
         <v>5</v>
@@ -7278,30 +7298,30 @@
         <v>74.53</v>
       </c>
       <c r="N92" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F93" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="G93" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>5</v>
@@ -7322,30 +7342,30 @@
         <v>42.28</v>
       </c>
       <c r="N93" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H94" s="4" t="n">
         <v>5</v>
@@ -7366,30 +7386,30 @@
         <v>0</v>
       </c>
       <c r="N94" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H95" s="4" t="n">
         <v>5</v>
@@ -7410,30 +7430,30 @@
         <v>58.46</v>
       </c>
       <c r="N95" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H96" s="4" t="n">
         <v>5</v>
@@ -7454,30 +7474,30 @@
         <v>217.24</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H97" s="4" t="n">
         <v>5</v>
@@ -7498,30 +7518,30 @@
         <v>2.3</v>
       </c>
       <c r="N97" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H98" s="4" t="n">
         <v>5</v>
@@ -7542,30 +7562,30 @@
         <v>0</v>
       </c>
       <c r="N98" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H99" s="4" t="n">
         <v>5</v>
@@ -7586,30 +7606,30 @@
         <v>0</v>
       </c>
       <c r="N99" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>5</v>
@@ -7630,30 +7650,30 @@
         <v>0</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H101" s="4" t="n">
         <v>5</v>
@@ -7674,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
